--- a/artfynd/A 29102-2024 artfynd.xlsx
+++ b/artfynd/A 29102-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97364839</v>
+        <v>120726733</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548617.3918256448</v>
+        <v>548648</v>
       </c>
       <c r="R2" t="n">
-        <v>6968035.045548229</v>
+        <v>6967981</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,62 +756,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97364838</v>
+        <v>120726799</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548592.2166972596</v>
+        <v>548707</v>
       </c>
       <c r="R3" t="n">
-        <v>6968035.586305911</v>
+        <v>6967953</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,31 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120726808</v>
+        <v>120726807</v>
       </c>
       <c r="B4" t="n">
-        <v>91431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548609</v>
+        <v>548591</v>
       </c>
       <c r="R4" t="n">
-        <v>6967997</v>
+        <v>6968001</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120726870</v>
+        <v>120726808</v>
       </c>
       <c r="B5" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548612</v>
+        <v>548609</v>
       </c>
       <c r="R5" t="n">
-        <v>6968076</v>
+        <v>6967997</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120726860</v>
+        <v>120726809</v>
       </c>
       <c r="B6" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1156,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548592</v>
+        <v>548597</v>
       </c>
       <c r="R6" t="n">
-        <v>6968015</v>
+        <v>6967992</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120726873</v>
+        <v>120726812</v>
       </c>
       <c r="B7" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548610</v>
+        <v>548660</v>
       </c>
       <c r="R7" t="n">
-        <v>6968010</v>
+        <v>6967939</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120726901</v>
+        <v>120726744</v>
       </c>
       <c r="B8" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548651</v>
+        <v>548565</v>
       </c>
       <c r="R8" t="n">
-        <v>6968036</v>
+        <v>6967968</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120726889</v>
+        <v>120726745</v>
       </c>
       <c r="B9" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548680</v>
+        <v>548548</v>
       </c>
       <c r="R9" t="n">
-        <v>6967977</v>
+        <v>6967983</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120726759</v>
+        <v>120726746</v>
       </c>
       <c r="B10" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1564,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548588</v>
+        <v>548569</v>
       </c>
       <c r="R10" t="n">
-        <v>6968049</v>
+        <v>6968022</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120726761</v>
+        <v>120726747</v>
       </c>
       <c r="B11" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1666,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548649</v>
+        <v>548678</v>
       </c>
       <c r="R11" t="n">
-        <v>6968014</v>
+        <v>6967985</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120726736</v>
+        <v>120726748</v>
       </c>
       <c r="B12" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1768,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548628</v>
+        <v>548631</v>
       </c>
       <c r="R12" t="n">
-        <v>6968033</v>
+        <v>6968017</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120726868</v>
+        <v>120726749</v>
       </c>
       <c r="B13" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1870,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548581</v>
+        <v>548710</v>
       </c>
       <c r="R13" t="n">
-        <v>6968067</v>
+        <v>6967978</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120726866</v>
+        <v>120726792</v>
       </c>
       <c r="B14" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1972,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548561</v>
+        <v>548558</v>
       </c>
       <c r="R14" t="n">
-        <v>6968120</v>
+        <v>6968026</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120726793</v>
+        <v>120726720</v>
       </c>
       <c r="B15" t="n">
-        <v>86233</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548665</v>
+        <v>548656</v>
       </c>
       <c r="R15" t="n">
-        <v>6967977</v>
+        <v>6967989</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120726785</v>
+        <v>120726721</v>
       </c>
       <c r="B16" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2176,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548645</v>
+        <v>548587</v>
       </c>
       <c r="R16" t="n">
-        <v>6967985</v>
+        <v>6968076</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120726882</v>
+        <v>120726793</v>
       </c>
       <c r="B17" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2278,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548650</v>
+        <v>548665</v>
       </c>
       <c r="R17" t="n">
-        <v>6967982</v>
+        <v>6967977</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120726794</v>
+        <v>120726780</v>
       </c>
       <c r="B18" t="n">
-        <v>88705</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4962</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2380,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548669</v>
+        <v>548546</v>
       </c>
       <c r="R18" t="n">
-        <v>6968018</v>
+        <v>6968026</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120726762</v>
+        <v>120726781</v>
       </c>
       <c r="B19" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2482,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548665</v>
+        <v>548560</v>
       </c>
       <c r="R19" t="n">
-        <v>6968013</v>
+        <v>6967999</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120726747</v>
+        <v>120726782</v>
       </c>
       <c r="B20" t="n">
-        <v>91974</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2560,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2584,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548678</v>
+        <v>548594</v>
       </c>
       <c r="R20" t="n">
-        <v>6967985</v>
+        <v>6968029</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2646,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120726867</v>
+        <v>120726783</v>
       </c>
       <c r="B21" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2686,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548569</v>
+        <v>548595</v>
       </c>
       <c r="R21" t="n">
-        <v>6968082</v>
+        <v>6968002</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2748,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120726786</v>
+        <v>120726785</v>
       </c>
       <c r="B22" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548670</v>
+        <v>548645</v>
       </c>
       <c r="R22" t="n">
-        <v>6967975</v>
+        <v>6967985</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2850,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120726721</v>
+        <v>120726786</v>
       </c>
       <c r="B23" t="n">
-        <v>86233</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2866,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3690</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2890,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548587</v>
+        <v>548670</v>
       </c>
       <c r="R23" t="n">
-        <v>6968076</v>
+        <v>6967975</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2952,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120726737</v>
+        <v>120726787</v>
       </c>
       <c r="B24" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2968,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2992,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548639</v>
+        <v>548689</v>
       </c>
       <c r="R24" t="n">
-        <v>6968031</v>
+        <v>6967968</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3054,37 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120726871</v>
+        <v>120726790</v>
       </c>
       <c r="B25" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3094,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548626</v>
+        <v>548532</v>
       </c>
       <c r="R25" t="n">
-        <v>6968051</v>
+        <v>6968096</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3156,37 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120726891</v>
+        <v>120726896</v>
       </c>
       <c r="B26" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3196,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548689</v>
+        <v>548697</v>
       </c>
       <c r="R26" t="n">
-        <v>6967968</v>
+        <v>6967942</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3258,37 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120726862</v>
+        <v>120726900</v>
       </c>
       <c r="B27" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3298,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548597</v>
+        <v>548596</v>
       </c>
       <c r="R27" t="n">
-        <v>6968043</v>
+        <v>6968028</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3360,15 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120726720</v>
+        <v>120726901</v>
       </c>
       <c r="B28" t="n">
-        <v>86233</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3376,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3400,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548656</v>
+        <v>548651</v>
       </c>
       <c r="R28" t="n">
-        <v>6967989</v>
+        <v>6968036</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3462,15 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120726748</v>
+        <v>97364838</v>
       </c>
       <c r="B29" t="n">
-        <v>91974</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3478,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3502,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548631</v>
+        <v>548592</v>
       </c>
       <c r="R29" t="n">
-        <v>6968017</v>
+        <v>6968036</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3532,12 +3359,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3552,27 +3379,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120726746</v>
+        <v>120726822</v>
       </c>
       <c r="B30" t="n">
-        <v>91974</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3580,21 +3406,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3604,10 +3430,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548569</v>
+        <v>548755</v>
       </c>
       <c r="R30" t="n">
-        <v>6968022</v>
+        <v>6967933</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3666,37 +3492,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120726799</v>
+        <v>120726823</v>
       </c>
       <c r="B31" t="n">
-        <v>91431</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3706,10 +3527,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548707</v>
+        <v>548733</v>
       </c>
       <c r="R31" t="n">
-        <v>6967953</v>
+        <v>6967928</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3768,19 +3589,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120726872</v>
+        <v>120726824</v>
       </c>
       <c r="B32" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3808,10 +3624,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548621</v>
+        <v>548727</v>
       </c>
       <c r="R32" t="n">
-        <v>6968042</v>
+        <v>6967943</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,15 +3686,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120726782</v>
+        <v>120726825</v>
       </c>
       <c r="B33" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3886,21 +3697,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3910,10 +3721,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548594</v>
+        <v>548722</v>
       </c>
       <c r="R33" t="n">
-        <v>6968029</v>
+        <v>6967952</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3972,15 +3783,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120726896</v>
+        <v>120726826</v>
       </c>
       <c r="B34" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3988,21 +3794,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4012,10 +3818,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548697</v>
+        <v>548714</v>
       </c>
       <c r="R34" t="n">
-        <v>6967942</v>
+        <v>6967961</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4074,15 +3880,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120726783</v>
+        <v>120726827</v>
       </c>
       <c r="B35" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4090,21 +3891,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4114,10 +3915,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548595</v>
+        <v>548551</v>
       </c>
       <c r="R35" t="n">
-        <v>6968002</v>
+        <v>6967977</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4176,37 +3977,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120726765</v>
+        <v>120726828</v>
       </c>
       <c r="B36" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4216,10 +4012,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548698</v>
+        <v>548537</v>
       </c>
       <c r="R36" t="n">
-        <v>6967974</v>
+        <v>6967988</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4278,19 +4074,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120726863</v>
+        <v>120726846</v>
       </c>
       <c r="B37" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4318,10 +4109,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548578</v>
+        <v>548573</v>
       </c>
       <c r="R37" t="n">
-        <v>6968055</v>
+        <v>6967963</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4380,19 +4171,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120726888</v>
+        <v>120726847</v>
       </c>
       <c r="B38" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4420,10 +4206,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548670</v>
+        <v>548538</v>
       </c>
       <c r="R38" t="n">
-        <v>6967976</v>
+        <v>6967986</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4482,19 +4268,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120726887</v>
+        <v>120726853</v>
       </c>
       <c r="B39" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4522,10 +4303,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548667</v>
+        <v>548501</v>
       </c>
       <c r="R39" t="n">
-        <v>6967959</v>
+        <v>6968090</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4584,37 +4365,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120726757</v>
+        <v>120726856</v>
       </c>
       <c r="B40" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4624,10 +4400,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548571</v>
+        <v>548552</v>
       </c>
       <c r="R40" t="n">
-        <v>6968019</v>
+        <v>6968022</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4686,15 +4462,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120726900</v>
+        <v>120726857</v>
       </c>
       <c r="B41" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4702,21 +4473,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4726,10 +4497,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548596</v>
+        <v>548546</v>
       </c>
       <c r="R41" t="n">
-        <v>6968028</v>
+        <v>6968026</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4788,37 +4559,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120726760</v>
+        <v>120726858</v>
       </c>
       <c r="B42" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4828,10 +4594,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548623</v>
+        <v>548537</v>
       </c>
       <c r="R42" t="n">
-        <v>6968084</v>
+        <v>6968021</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4890,15 +4656,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120726781</v>
+        <v>120726859</v>
       </c>
       <c r="B43" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4906,21 +4667,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4930,10 +4691,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548560</v>
+        <v>548548</v>
       </c>
       <c r="R43" t="n">
-        <v>6967999</v>
+        <v>6967983</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4992,15 +4753,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120726715</v>
+        <v>120726860</v>
       </c>
       <c r="B44" t="n">
-        <v>88532</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5008,21 +4764,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5032,10 +4788,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548603</v>
+        <v>548592</v>
       </c>
       <c r="R44" t="n">
-        <v>6968074</v>
+        <v>6968015</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5094,15 +4850,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120726735</v>
+        <v>120726861</v>
       </c>
       <c r="B45" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5110,21 +4861,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5134,10 +4885,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548621</v>
+        <v>548593</v>
       </c>
       <c r="R45" t="n">
-        <v>6968044</v>
+        <v>6968034</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5196,19 +4947,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120726825</v>
+        <v>120726862</v>
       </c>
       <c r="B46" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5236,10 +4982,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548722</v>
+        <v>548597</v>
       </c>
       <c r="R46" t="n">
-        <v>6967952</v>
+        <v>6968043</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5298,15 +5044,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120726716</v>
+        <v>120726863</v>
       </c>
       <c r="B47" t="n">
-        <v>88532</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5314,21 +5055,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5338,10 +5079,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548628</v>
+        <v>548578</v>
       </c>
       <c r="R47" t="n">
-        <v>6968042</v>
+        <v>6968055</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5400,37 +5141,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120726758</v>
+        <v>120726864</v>
       </c>
       <c r="B48" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5440,10 +5176,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548597</v>
+        <v>548568</v>
       </c>
       <c r="R48" t="n">
-        <v>6968026</v>
+        <v>6968057</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5502,15 +5238,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120726739</v>
+        <v>120726865</v>
       </c>
       <c r="B49" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5518,21 +5249,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5542,10 +5273,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548678</v>
+        <v>548567</v>
       </c>
       <c r="R49" t="n">
-        <v>6967985</v>
+        <v>6968079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5604,15 +5335,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120726787</v>
+        <v>120726866</v>
       </c>
       <c r="B50" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5620,21 +5346,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5644,10 +5370,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548689</v>
+        <v>548561</v>
       </c>
       <c r="R50" t="n">
-        <v>6967968</v>
+        <v>6968120</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5706,19 +5432,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120726879</v>
+        <v>120726867</v>
       </c>
       <c r="B51" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5746,10 +5467,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548653</v>
+        <v>548569</v>
       </c>
       <c r="R51" t="n">
-        <v>6968039</v>
+        <v>6968082</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5808,15 +5529,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120726749</v>
+        <v>120726868</v>
       </c>
       <c r="B52" t="n">
-        <v>91974</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5824,21 +5540,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5848,10 +5564,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548710</v>
+        <v>548581</v>
       </c>
       <c r="R52" t="n">
-        <v>6967978</v>
+        <v>6968067</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5910,15 +5626,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120726796</v>
+        <v>120726870</v>
       </c>
       <c r="B53" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5926,21 +5637,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5950,10 +5661,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548598</v>
+        <v>548612</v>
       </c>
       <c r="R53" t="n">
-        <v>6968080</v>
+        <v>6968076</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6012,19 +5723,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120726824</v>
+        <v>120726871</v>
       </c>
       <c r="B54" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6052,10 +5758,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548727</v>
+        <v>548626</v>
       </c>
       <c r="R54" t="n">
-        <v>6967943</v>
+        <v>6968051</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6114,37 +5820,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120726733</v>
+        <v>120726872</v>
       </c>
       <c r="B55" t="n">
-        <v>91946</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>149</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6154,10 +5855,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548648</v>
+        <v>548621</v>
       </c>
       <c r="R55" t="n">
-        <v>6967981</v>
+        <v>6968042</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6216,19 +5917,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120726823</v>
+        <v>120726873</v>
       </c>
       <c r="B56" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6256,10 +5952,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548733</v>
+        <v>548610</v>
       </c>
       <c r="R56" t="n">
-        <v>6967928</v>
+        <v>6968010</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6318,15 +6014,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120726740</v>
+        <v>120726874</v>
       </c>
       <c r="B57" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6334,21 +6025,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6358,10 +6049,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548613</v>
+        <v>548610</v>
       </c>
       <c r="R57" t="n">
-        <v>6968032</v>
+        <v>6968007</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6420,15 +6111,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120726734</v>
+        <v>120726875</v>
       </c>
       <c r="B58" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6436,21 +6122,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6460,10 +6146,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548598</v>
+        <v>548585</v>
       </c>
       <c r="R58" t="n">
-        <v>6968017</v>
+        <v>6967987</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6522,19 +6208,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120726878</v>
+        <v>120726877</v>
       </c>
       <c r="B59" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6562,10 +6243,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548638</v>
+        <v>548622</v>
       </c>
       <c r="R59" t="n">
-        <v>6968000</v>
+        <v>6967983</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6624,19 +6305,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120726826</v>
+        <v>120726878</v>
       </c>
       <c r="B60" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -6664,10 +6340,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548714</v>
+        <v>548638</v>
       </c>
       <c r="R60" t="n">
-        <v>6967961</v>
+        <v>6968000</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6726,37 +6402,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120726807</v>
+        <v>120726879</v>
       </c>
       <c r="B61" t="n">
-        <v>91431</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6766,10 +6437,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548591</v>
+        <v>548653</v>
       </c>
       <c r="R61" t="n">
-        <v>6968001</v>
+        <v>6968039</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6828,19 +6499,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120726861</v>
+        <v>120726880</v>
       </c>
       <c r="B62" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -6868,10 +6534,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548593</v>
+        <v>548665</v>
       </c>
       <c r="R62" t="n">
-        <v>6968034</v>
+        <v>6968013</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6933,16 +6599,11 @@
         <v>120726881</v>
       </c>
       <c r="B63" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -7032,19 +6693,14 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120726880</v>
+        <v>120726882</v>
       </c>
       <c r="B64" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -7072,10 +6728,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548665</v>
+        <v>548650</v>
       </c>
       <c r="R64" t="n">
-        <v>6968013</v>
+        <v>6967982</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7134,19 +6790,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120726890</v>
+        <v>120726883</v>
       </c>
       <c r="B65" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -7174,10 +6825,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>548686</v>
+        <v>548644</v>
       </c>
       <c r="R65" t="n">
-        <v>6967995</v>
+        <v>6967969</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7236,19 +6887,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120726893</v>
+        <v>120726884</v>
       </c>
       <c r="B66" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -7276,10 +6922,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548700</v>
+        <v>548643</v>
       </c>
       <c r="R66" t="n">
-        <v>6967990</v>
+        <v>6967952</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7338,19 +6984,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120726864</v>
+        <v>120726885</v>
       </c>
       <c r="B67" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -7378,10 +7019,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548568</v>
+        <v>548642</v>
       </c>
       <c r="R67" t="n">
-        <v>6968057</v>
+        <v>6967949</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7440,19 +7081,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120726865</v>
+        <v>120726887</v>
       </c>
       <c r="B68" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -7480,10 +7116,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548567</v>
+        <v>548667</v>
       </c>
       <c r="R68" t="n">
-        <v>6968079</v>
+        <v>6967959</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7542,37 +7178,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120726767</v>
+        <v>120726888</v>
       </c>
       <c r="B69" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7582,10 +7213,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548678</v>
+        <v>548670</v>
       </c>
       <c r="R69" t="n">
-        <v>6967956</v>
+        <v>6967976</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7644,19 +7275,14 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120726874</v>
+        <v>120726889</v>
       </c>
       <c r="B70" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -7684,10 +7310,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548610</v>
+        <v>548680</v>
       </c>
       <c r="R70" t="n">
-        <v>6968007</v>
+        <v>6967977</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7746,15 +7372,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120726795</v>
+        <v>120726890</v>
       </c>
       <c r="B71" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7762,21 +7383,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7786,10 +7407,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548571</v>
+        <v>548686</v>
       </c>
       <c r="R71" t="n">
-        <v>6968097</v>
+        <v>6967995</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7845,6 +7466,2343 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120726891</v>
+      </c>
+      <c r="B72" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>548689</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6967968</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120726892</v>
+      </c>
+      <c r="B73" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>548668</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6967930</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120726893</v>
+      </c>
+      <c r="B74" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>548700</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6967990</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>120726750</v>
+      </c>
+      <c r="B75" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>548537</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6967985</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>120726757</v>
+      </c>
+      <c r="B76" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>548571</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6968019</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>120726758</v>
+      </c>
+      <c r="B77" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>548597</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6968026</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120726759</v>
+      </c>
+      <c r="B78" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>548588</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6968049</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120726760</v>
+      </c>
+      <c r="B79" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>548623</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6968084</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120726761</v>
+      </c>
+      <c r="B80" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>548649</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6968014</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120726762</v>
+      </c>
+      <c r="B81" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>548665</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6968013</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120726763</v>
+      </c>
+      <c r="B82" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>548644</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6967969</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120726765</v>
+      </c>
+      <c r="B83" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>548698</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6967974</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120726767</v>
+      </c>
+      <c r="B84" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>548678</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6967956</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120726715</v>
+      </c>
+      <c r="B85" t="n">
+        <v>89156</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>548603</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6968074</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>120726716</v>
+      </c>
+      <c r="B86" t="n">
+        <v>89156</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>548628</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6968042</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>120726794</v>
+      </c>
+      <c r="B87" t="n">
+        <v>90522</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>548669</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6968018</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>120726743</v>
+      </c>
+      <c r="B88" t="n">
+        <v>93181</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>548660</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6967930</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>97364839</v>
+      </c>
+      <c r="B89" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>548617</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6968035</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2021-10-10</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2021-10-10</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>120726795</v>
+      </c>
+      <c r="B90" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>548571</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6968097</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>120726796</v>
+      </c>
+      <c r="B91" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>548598</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6968080</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120726725</v>
+      </c>
+      <c r="B92" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>548658</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6967943</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>120726728</v>
+      </c>
+      <c r="B93" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>548773</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6967926</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>120726730</v>
+      </c>
+      <c r="B94" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>548592</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6967992</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>120726732</v>
+      </c>
+      <c r="B95" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>548668</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6967932</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29102-2024 artfynd.xlsx
+++ b/artfynd/A 29102-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AZ95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726733</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726799</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726807</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726808</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726809</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726812</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726744</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726745</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726746</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726747</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726748</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726749</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726792</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726720</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726721</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726793</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726780</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726781</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726782</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726783</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726785</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726786</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726787</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726790</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726896</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726900</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726901</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3392,6 +3532,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364838</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3489,6 +3634,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726822</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3586,6 +3736,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726823</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3683,6 +3838,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726824</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3780,6 +3940,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726825</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3877,6 +4042,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726826</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3974,6 +4144,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726827</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4071,6 +4246,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726828</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4168,6 +4348,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726846</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4265,6 +4450,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726847</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4362,6 +4552,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726853</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4459,6 +4654,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726856</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4556,6 +4756,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726857</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4653,6 +4858,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726858</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4750,6 +4960,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726859</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4847,6 +5062,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726860</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4944,6 +5164,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726861</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5041,6 +5266,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726862</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5138,6 +5368,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726863</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5235,6 +5470,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726864</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5332,6 +5572,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726865</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5429,6 +5674,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726866</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5526,6 +5776,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726867</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5623,6 +5878,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726868</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5720,6 +5980,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726870</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5817,6 +6082,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726871</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5914,6 +6184,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726872</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6011,6 +6286,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726873</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6108,6 +6388,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726874</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6205,6 +6490,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726875</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6302,6 +6592,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726877</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6399,6 +6694,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726878</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6496,6 +6796,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726879</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6593,6 +6898,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726880</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6690,6 +7000,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726881</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6787,6 +7102,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726882</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6884,6 +7204,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726883</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6981,6 +7306,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726884</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7078,6 +7408,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726885</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7175,6 +7510,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726887</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7272,6 +7612,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726888</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7369,6 +7714,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726889</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7466,6 +7816,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726890</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7563,6 +7918,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726891</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7660,6 +8020,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726892</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7757,6 +8122,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726893</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7854,6 +8224,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726750</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7951,6 +8326,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726757</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8048,6 +8428,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726758</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8145,6 +8530,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726759</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8242,6 +8632,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726760</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8339,6 +8734,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726761</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8436,6 +8836,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726762</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8533,6 +8938,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726763</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8630,6 +9040,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726765</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8727,6 +9142,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726767</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8824,6 +9244,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726715</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8921,6 +9346,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726716</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9018,6 +9448,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726794</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9115,6 +9550,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726743</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9221,6 +9661,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364839</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9318,6 +9763,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726795</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9415,6 +9865,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726796</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9512,6 +9967,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726725</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9609,6 +10069,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726728</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9706,6 +10171,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726730</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9803,8 +10273,109 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726732</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>